--- a/results/block2_results/area/Normal_2/branches/dataframes/dataset_LCA_B05_Normal_2.xlsx
+++ b/results/block2_results/area/Normal_2/branches/dataframes/dataset_LCA_B05_Normal_2.xlsx
@@ -523,7 +523,7 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1865502853357017</v>
+        <v>0.1865600545781031</v>
       </c>
     </row>
     <row r="3">
@@ -564,7 +564,7 @@
         <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9027069616915873</v>
+        <v>0.9025130183448353</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>1.329790079151363</v>
+        <v>1.329840539349983</v>
       </c>
     </row>
     <row r="5">
@@ -646,7 +646,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45343381859624</v>
+        <v>3.466416537272089</v>
       </c>
     </row>
     <row r="6">
@@ -687,7 +687,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45343381859624</v>
+        <v>3.466416537272089</v>
       </c>
     </row>
     <row r="7">
@@ -728,7 +728,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>5.333486823954726</v>
+        <v>5.331086360382172</v>
       </c>
     </row>
     <row r="8">
@@ -769,7 +769,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>6.042760034830393</v>
+        <v>6.039954809969425</v>
       </c>
     </row>
     <row r="9">
@@ -810,7 +810,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>9.774211633003286</v>
+        <v>9.635797748144768</v>
       </c>
     </row>
     <row r="10">
@@ -851,7 +851,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>10.47404150664014</v>
+        <v>10.47449632497913</v>
       </c>
     </row>
     <row r="11">
@@ -892,7 +892,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>10.50943319366649</v>
+        <v>10.50475136658863</v>
       </c>
     </row>
     <row r="12">
@@ -933,7 +933,7 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>12.00213237476259</v>
+        <v>11.98254064055079</v>
       </c>
     </row>
     <row r="13">
@@ -974,7 +974,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>12.00213237476259</v>
+        <v>11.98254064055079</v>
       </c>
     </row>
     <row r="14">
@@ -1015,7 +1015,7 @@
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>12.33737930054762</v>
+        <v>12.33786735892068</v>
       </c>
     </row>
     <row r="15">
@@ -1056,7 +1056,7 @@
         <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>1.112358201660258</v>
+        <v>1.112431640076021</v>
       </c>
     </row>
     <row r="16">
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>1.062777698332418</v>
+        <v>1.063099514135826</v>
       </c>
     </row>
     <row r="17">
@@ -1138,7 +1138,7 @@
         <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5772589909199825</v>
+        <v>0.5792498871576799</v>
       </c>
     </row>
     <row r="18">
@@ -1179,7 +1179,7 @@
         <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>15.92122532206255</v>
+        <v>16.08614487448754</v>
       </c>
     </row>
     <row r="19">
@@ -1220,7 +1220,7 @@
         <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>15.92244207042752</v>
+        <v>15.9224055805709</v>
       </c>
     </row>
     <row r="20">
@@ -1261,7 +1261,7 @@
         <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>15.90440478338968</v>
+        <v>15.90529663782263</v>
       </c>
     </row>
     <row r="21">
@@ -1302,7 +1302,7 @@
         <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>15.90440478338968</v>
+        <v>15.90529663782263</v>
       </c>
     </row>
     <row r="22">
@@ -1343,7 +1343,7 @@
         <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>15.95062527901377</v>
+        <v>15.94907264007682</v>
       </c>
     </row>
     <row r="23">
@@ -1384,7 +1384,7 @@
         <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>16.47241871755802</v>
+        <v>16.46917095811485</v>
       </c>
     </row>
     <row r="24">
@@ -1425,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>16.47241871755802</v>
+        <v>16.46917095811485</v>
       </c>
     </row>
     <row r="25">
@@ -1466,7 +1466,7 @@
         <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>16.68125211750191</v>
+        <v>16.68150359318814</v>
       </c>
     </row>
     <row r="26">
@@ -1507,7 +1507,7 @@
         <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>17.13662195006867</v>
+        <v>17.13699864778113</v>
       </c>
     </row>
     <row r="27">
@@ -1548,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>17.65643758803501</v>
+        <v>17.65606000717672</v>
       </c>
     </row>
     <row r="28">
@@ -1589,7 +1589,7 @@
         <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>17.726221843046</v>
+        <v>17.72686803633449</v>
       </c>
     </row>
     <row r="29">
@@ -1630,7 +1630,7 @@
         <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>17.81936612530993</v>
+        <v>17.81944109171629</v>
       </c>
     </row>
     <row r="30">
@@ -1671,7 +1671,7 @@
         <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>17.83069852722052</v>
+        <v>17.82989940170764</v>
       </c>
     </row>
     <row r="31">
@@ -1712,7 +1712,7 @@
         <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>17.91045501285387</v>
+        <v>17.91105143658421</v>
       </c>
     </row>
     <row r="32">
@@ -1753,7 +1753,7 @@
         <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>18.11075800455528</v>
+        <v>18.11063187715624</v>
       </c>
     </row>
     <row r="33">
@@ -1794,7 +1794,7 @@
         <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>18.15983980085726</v>
+        <v>18.15987093947113</v>
       </c>
     </row>
     <row r="34">
@@ -1835,7 +1835,7 @@
         <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>18.15983980085726</v>
+        <v>18.15987093947113</v>
       </c>
     </row>
     <row r="35">
@@ -1876,7 +1876,7 @@
         <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>18.25333437977661</v>
+        <v>18.25347872265014</v>
       </c>
     </row>
     <row r="36">
@@ -1917,7 +1917,7 @@
         <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>18.31313623191253</v>
+        <v>18.31300880162258</v>
       </c>
     </row>
     <row r="37">
@@ -1958,7 +1958,7 @@
         <v>5</v>
       </c>
       <c r="K37" t="n">
-        <v>18.19251281614148</v>
+        <v>18.18374248726346</v>
       </c>
     </row>
     <row r="38">
@@ -1999,7 +1999,7 @@
         <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>18.32725138968634</v>
+        <v>18.32489867741947</v>
       </c>
     </row>
     <row r="39">
@@ -2040,7 +2040,7 @@
         <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>18.32725138968634</v>
+        <v>18.32489867741947</v>
       </c>
     </row>
     <row r="40">
@@ -2081,7 +2081,7 @@
         <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>18.43101520147438</v>
+        <v>18.43115021407112</v>
       </c>
     </row>
     <row r="41">
@@ -2122,7 +2122,7 @@
         <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>18.5685952563802</v>
+        <v>18.56838849707095</v>
       </c>
     </row>
     <row r="42">
@@ -2163,7 +2163,7 @@
         <v>5</v>
       </c>
       <c r="K42" t="n">
-        <v>18.58008141167307</v>
+        <v>18.58191783635835</v>
       </c>
     </row>
     <row r="43">
@@ -2204,7 +2204,7 @@
         <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>18.83955821569582</v>
+        <v>18.84045488162381</v>
       </c>
     </row>
     <row r="44">
@@ -2245,7 +2245,7 @@
         <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>18.7683839298948</v>
+        <v>18.76887581351305</v>
       </c>
     </row>
     <row r="45">
@@ -2286,7 +2286,7 @@
         <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>18.73776743207468</v>
+        <v>18.74229667334115</v>
       </c>
     </row>
     <row r="46">
@@ -2327,7 +2327,7 @@
         <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>18.54743048859889</v>
+        <v>18.54653760366034</v>
       </c>
     </row>
     <row r="47">
@@ -2368,7 +2368,7 @@
         <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>18.15252804766378</v>
+        <v>18.15454817016082</v>
       </c>
     </row>
     <row r="48">
@@ -2409,7 +2409,7 @@
         <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>18.08003792003841</v>
+        <v>18.08007013293001</v>
       </c>
     </row>
     <row r="49">
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="K49" t="n">
-        <v>18.0508829171354</v>
+        <v>18.04915627873921</v>
       </c>
     </row>
     <row r="50">
@@ -2491,7 +2491,7 @@
         <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>17.99032586218531</v>
+        <v>17.98837875632599</v>
       </c>
     </row>
     <row r="51">
@@ -2532,7 +2532,7 @@
         <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>17.99032586218531</v>
+        <v>17.98837875632599</v>
       </c>
     </row>
     <row r="52">
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="K52" t="n">
-        <v>17.7490806393877</v>
+        <v>17.74861576103778</v>
       </c>
     </row>
     <row r="53">
@@ -2614,7 +2614,7 @@
         <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>17.74969718700408</v>
+        <v>17.74812266773921</v>
       </c>
     </row>
     <row r="54">
@@ -2655,7 +2655,7 @@
         <v>5</v>
       </c>
       <c r="K54" t="n">
-        <v>17.74969718700408</v>
+        <v>17.74812266773921</v>
       </c>
     </row>
     <row r="55">
@@ -2696,7 +2696,7 @@
         <v>5</v>
       </c>
       <c r="K55" t="n">
-        <v>17.81814662802715</v>
+        <v>17.79881074691802</v>
       </c>
     </row>
     <row r="56">
@@ -2737,7 +2737,7 @@
         <v>5</v>
       </c>
       <c r="K56" t="n">
-        <v>17.99225470919088</v>
+        <v>17.97859383075771</v>
       </c>
     </row>
     <row r="57">
@@ -2778,7 +2778,7 @@
         <v>5</v>
       </c>
       <c r="K57" t="n">
-        <v>18.04864477364506</v>
+        <v>18.04209307204975</v>
       </c>
     </row>
     <row r="58">
@@ -2819,7 +2819,7 @@
         <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>18.06393349092241</v>
+        <v>18.05583693465113</v>
       </c>
     </row>
     <row r="59">
@@ -2860,7 +2860,7 @@
         <v>5</v>
       </c>
       <c r="K59" t="n">
-        <v>18.25587384616591</v>
+        <v>18.25537619819129</v>
       </c>
     </row>
     <row r="60">
@@ -2901,7 +2901,7 @@
         <v>5</v>
       </c>
       <c r="K60" t="n">
-        <v>18.25587384616591</v>
+        <v>18.25537619819129</v>
       </c>
     </row>
     <row r="61">
@@ -2942,7 +2942,7 @@
         <v>5</v>
       </c>
       <c r="K61" t="n">
-        <v>18.26553935250956</v>
+        <v>18.26535630570529</v>
       </c>
     </row>
     <row r="62">
@@ -2983,7 +2983,7 @@
         <v>5</v>
       </c>
       <c r="K62" t="n">
-        <v>18.25615665036968</v>
+        <v>18.25543714052691</v>
       </c>
     </row>
     <row r="63">
@@ -3024,7 +3024,7 @@
         <v>5</v>
       </c>
       <c r="K63" t="n">
-        <v>18.32865305918012</v>
+        <v>18.35082486847733</v>
       </c>
     </row>
     <row r="64">
@@ -3065,7 +3065,7 @@
         <v>5</v>
       </c>
       <c r="K64" t="n">
-        <v>18.22115293721825</v>
+        <v>18.31842442556919</v>
       </c>
     </row>
     <row r="65">
@@ -3106,7 +3106,7 @@
         <v>5</v>
       </c>
       <c r="K65" t="n">
-        <v>18.33354581660341</v>
+        <v>18.3533122614999</v>
       </c>
     </row>
     <row r="66">
@@ -3147,7 +3147,7 @@
         <v>5</v>
       </c>
       <c r="K66" t="n">
-        <v>18.33354581660341</v>
+        <v>18.3533122614999</v>
       </c>
     </row>
     <row r="67">
@@ -3188,7 +3188,7 @@
         <v>5</v>
       </c>
       <c r="K67" t="n">
-        <v>19.39058911605064</v>
+        <v>18.98502910614225</v>
       </c>
     </row>
     <row r="68">
@@ -3229,7 +3229,7 @@
         <v>5</v>
       </c>
       <c r="K68" t="n">
-        <v>19.39058911605064</v>
+        <v>18.98502910614225</v>
       </c>
     </row>
     <row r="69">
@@ -3270,7 +3270,7 @@
         <v>5</v>
       </c>
       <c r="K69" t="n">
-        <v>19.39058911605064</v>
+        <v>18.98502910614225</v>
       </c>
     </row>
     <row r="70">
@@ -3311,7 +3311,7 @@
         <v>5</v>
       </c>
       <c r="K70" t="n">
-        <v>21.66404939438216</v>
+        <v>20.94651363125861</v>
       </c>
     </row>
     <row r="71">
@@ -3352,7 +3352,7 @@
         <v>5</v>
       </c>
       <c r="K71" t="n">
-        <v>21.66404939438216</v>
+        <v>20.94651363125861</v>
       </c>
     </row>
     <row r="72">
@@ -3393,7 +3393,7 @@
         <v>6</v>
       </c>
       <c r="K72" t="n">
-        <v>22.14156626639458</v>
+        <v>21.90771317294598</v>
       </c>
     </row>
     <row r="73">
@@ -3434,7 +3434,7 @@
         <v>6</v>
       </c>
       <c r="K73" t="n">
-        <v>22.16242471488815</v>
+        <v>21.95699867896413</v>
       </c>
     </row>
     <row r="74">
@@ -3475,7 +3475,7 @@
         <v>6</v>
       </c>
       <c r="K74" t="n">
-        <v>23.89073664208809</v>
+        <v>23.78508316000404</v>
       </c>
     </row>
     <row r="75">
@@ -3516,7 +3516,7 @@
         <v>6</v>
       </c>
       <c r="K75" t="n">
-        <v>0.6742643271988668</v>
+        <v>0.6687806371559569</v>
       </c>
     </row>
     <row r="76">
@@ -3557,7 +3557,7 @@
         <v>6</v>
       </c>
       <c r="K76" t="n">
-        <v>0.7252819316670009</v>
+        <v>0.7213389540098346</v>
       </c>
     </row>
     <row r="77">
@@ -3598,7 +3598,7 @@
         <v>6</v>
       </c>
       <c r="K77" t="n">
-        <v>0.7819875890269926</v>
+        <v>0.7791062941235075</v>
       </c>
     </row>
     <row r="78">
@@ -3639,7 +3639,7 @@
         <v>6</v>
       </c>
       <c r="K78" t="n">
-        <v>0.8103286190362372</v>
+        <v>0.8050203406469022</v>
       </c>
     </row>
     <row r="79">
@@ -3680,7 +3680,7 @@
         <v>6</v>
       </c>
       <c r="K79" t="n">
-        <v>25.14243936608069</v>
+        <v>25.09856616014096</v>
       </c>
     </row>
     <row r="80">
@@ -3721,7 +3721,7 @@
         <v>6</v>
       </c>
       <c r="K80" t="n">
-        <v>26.08450755720653</v>
+        <v>26.2404020349576</v>
       </c>
     </row>
     <row r="81">
@@ -3762,7 +3762,7 @@
         <v>6</v>
       </c>
       <c r="K81" t="n">
-        <v>26.27248005679646</v>
+        <v>26.2404020349576</v>
       </c>
     </row>
     <row r="82">
@@ -3803,7 +3803,7 @@
         <v>6</v>
       </c>
       <c r="K82" t="n">
-        <v>28.07173518406669</v>
+        <v>28.15250810073567</v>
       </c>
     </row>
     <row r="83">
@@ -3844,7 +3844,7 @@
         <v>11</v>
       </c>
       <c r="K83" t="n">
-        <v>30.02397104987351</v>
+        <v>30.0723175916815</v>
       </c>
     </row>
     <row r="84">
@@ -3885,7 +3885,7 @@
         <v>11</v>
       </c>
       <c r="K84" t="n">
-        <v>33.93106343073827</v>
+        <v>33.12970607485668</v>
       </c>
     </row>
     <row r="85">
@@ -3926,7 +3926,7 @@
         <v>11</v>
       </c>
       <c r="K85" t="n">
-        <v>33.93106343073827</v>
+        <v>33.12970607485668</v>
       </c>
     </row>
     <row r="86">
@@ -3967,7 +3967,7 @@
         <v>11</v>
       </c>
       <c r="K86" t="n">
-        <v>35.72995783874642</v>
+        <v>35.33464815617634</v>
       </c>
     </row>
     <row r="87">
@@ -4008,7 +4008,7 @@
         <v>11</v>
       </c>
       <c r="K87" t="n">
-        <v>35.55938049603233</v>
+        <v>35.33464815617634</v>
       </c>
     </row>
     <row r="88">
@@ -4049,7 +4049,7 @@
         <v>11</v>
       </c>
       <c r="K88" t="n">
-        <v>34.26020823081542</v>
+        <v>34.32751082832033</v>
       </c>
     </row>
     <row r="89">
@@ -4090,7 +4090,7 @@
         <v>11</v>
       </c>
       <c r="K89" t="n">
-        <v>34.26020823081542</v>
+        <v>33.72263094040903</v>
       </c>
     </row>
     <row r="90">
@@ -4131,7 +4131,7 @@
         <v>11</v>
       </c>
       <c r="K90" t="n">
-        <v>33.60421491792203</v>
+        <v>33.58353956337891</v>
       </c>
     </row>
     <row r="91">
@@ -4172,7 +4172,7 @@
         <v>11</v>
       </c>
       <c r="K91" t="n">
-        <v>32.25732494002654</v>
+        <v>32.46181745415356</v>
       </c>
     </row>
     <row r="92">
@@ -4213,7 +4213,7 @@
         <v>11</v>
       </c>
       <c r="K92" t="n">
-        <v>32.25732494002654</v>
+        <v>31.53057840703528</v>
       </c>
     </row>
     <row r="93">
@@ -4254,7 +4254,7 @@
         <v>11</v>
       </c>
       <c r="K93" t="n">
-        <v>29.5809159019295</v>
+        <v>29.64732090098634</v>
       </c>
     </row>
     <row r="94">
@@ -4295,7 +4295,7 @@
         <v>11</v>
       </c>
       <c r="K94" t="n">
-        <v>28.85260555578949</v>
+        <v>28.84728032399684</v>
       </c>
     </row>
     <row r="95">
@@ -4336,7 +4336,7 @@
         <v>11</v>
       </c>
       <c r="K95" t="n">
-        <v>27.59102216091332</v>
+        <v>27.68572614297149</v>
       </c>
     </row>
     <row r="96">
@@ -4377,7 +4377,7 @@
         <v>11</v>
       </c>
       <c r="K96" t="n">
-        <v>13.58206214581482</v>
+        <v>13.45582952174553</v>
       </c>
     </row>
     <row r="97">
@@ -4418,7 +4418,7 @@
         <v>11</v>
       </c>
       <c r="K97" t="n">
-        <v>14.92850198125039</v>
+        <v>14.92454405059119</v>
       </c>
     </row>
     <row r="98">
@@ -4459,7 +4459,7 @@
         <v>11</v>
       </c>
       <c r="K98" t="n">
-        <v>17.63710851302559</v>
+        <v>17.55510645238489</v>
       </c>
     </row>
     <row r="99">
@@ -4500,7 +4500,7 @@
         <v>11</v>
       </c>
       <c r="K99" t="n">
-        <v>32.50207028708833</v>
+        <v>32.67655883920442</v>
       </c>
     </row>
     <row r="100">
@@ -4541,7 +4541,7 @@
         <v>11</v>
       </c>
       <c r="K100" t="n">
-        <v>32.8854867991345</v>
+        <v>32.67655883920442</v>
       </c>
     </row>
     <row r="101">
@@ -4582,7 +4582,7 @@
         <v>11</v>
       </c>
       <c r="K101" t="n">
-        <v>34.04385643174101</v>
+        <v>34.18326497614485</v>
       </c>
     </row>
     <row r="102">
@@ -4623,7 +4623,7 @@
         <v>11</v>
       </c>
       <c r="K102" t="n">
-        <v>34.8005884430348</v>
+        <v>26.30341888026399</v>
       </c>
     </row>
     <row r="103">
@@ -4664,7 +4664,7 @@
         <v>11</v>
       </c>
       <c r="K103" t="n">
-        <v>34.8005884430348</v>
+        <v>26.30341888026399</v>
       </c>
     </row>
     <row r="104">
@@ -4705,7 +4705,7 @@
         <v>11</v>
       </c>
       <c r="K104" t="n">
-        <v>26.65020320706951</v>
+        <v>29.28176759456571</v>
       </c>
     </row>
     <row r="105">
@@ -4746,7 +4746,7 @@
         <v>11</v>
       </c>
       <c r="K105" t="n">
-        <v>26.65020320706951</v>
+        <v>29.28176759456571</v>
       </c>
     </row>
     <row r="106">
@@ -4787,7 +4787,7 @@
         <v>11</v>
       </c>
       <c r="K106" t="n">
-        <v>30.47228368650138</v>
+        <v>29.69263070332197</v>
       </c>
     </row>
     <row r="107">
@@ -4828,7 +4828,7 @@
         <v>11</v>
       </c>
       <c r="K107" t="n">
-        <v>30.47228368650138</v>
+        <v>29.69263070332197</v>
       </c>
     </row>
     <row r="108">
@@ -4869,7 +4869,7 @@
         <v>11</v>
       </c>
       <c r="K108" t="n">
-        <v>31.57247686638782</v>
+        <v>30.9277383207447</v>
       </c>
     </row>
     <row r="109">
@@ -4910,7 +4910,7 @@
         <v>11</v>
       </c>
       <c r="K109" t="n">
-        <v>30.7051003580383</v>
+        <v>30.48736325109561</v>
       </c>
     </row>
     <row r="110">
@@ -4951,7 +4951,7 @@
         <v>11</v>
       </c>
       <c r="K110" t="n">
-        <v>29.97582284390176</v>
+        <v>29.8339701431021</v>
       </c>
     </row>
     <row r="111">
@@ -4992,7 +4992,7 @@
         <v>11</v>
       </c>
       <c r="K111" t="n">
-        <v>29.97582284390176</v>
+        <v>29.8339701431021</v>
       </c>
     </row>
     <row r="112">
@@ -5033,7 +5033,7 @@
         <v>17</v>
       </c>
       <c r="K112" t="n">
-        <v>27.54307712829354</v>
+        <v>29.97422687701681</v>
       </c>
     </row>
     <row r="113">
@@ -5074,7 +5074,7 @@
         <v>17</v>
       </c>
       <c r="K113" t="n">
-        <v>6.368860332302354</v>
+        <v>6.394229628251723</v>
       </c>
     </row>
     <row r="114">
@@ -5115,7 +5115,7 @@
         <v>17</v>
       </c>
       <c r="K114" t="n">
-        <v>6.243578717985123</v>
+        <v>6.260133337315924</v>
       </c>
     </row>
     <row r="115">
@@ -5156,7 +5156,7 @@
         <v>17</v>
       </c>
       <c r="K115" t="n">
-        <v>6.32730569450491</v>
+        <v>6.304330365346789</v>
       </c>
     </row>
     <row r="116">
@@ -5197,7 +5197,7 @@
         <v>17</v>
       </c>
       <c r="K116" t="n">
-        <v>6.32730569450491</v>
+        <v>6.304330365346789</v>
       </c>
     </row>
     <row r="117">
@@ -5238,7 +5238,7 @@
         <v>17</v>
       </c>
       <c r="K117" t="n">
-        <v>6.392435803687235</v>
+        <v>6.387273696259207</v>
       </c>
     </row>
     <row r="118">
@@ -5279,7 +5279,7 @@
         <v>17</v>
       </c>
       <c r="K118" t="n">
-        <v>6.47837896333867</v>
+        <v>6.45604406382135</v>
       </c>
     </row>
     <row r="119">
@@ -5320,7 +5320,7 @@
         <v>17</v>
       </c>
       <c r="K119" t="n">
-        <v>6.811497567267673</v>
+        <v>6.818788451684092</v>
       </c>
     </row>
     <row r="120">
@@ -5361,7 +5361,7 @@
         <v>17</v>
       </c>
       <c r="K120" t="n">
-        <v>6.811497567267673</v>
+        <v>6.818788451684092</v>
       </c>
     </row>
     <row r="121">
@@ -5402,7 +5402,7 @@
         <v>17</v>
       </c>
       <c r="K121" t="n">
-        <v>6.90473503174959</v>
+        <v>6.892426842023912</v>
       </c>
     </row>
     <row r="122">
@@ -5443,7 +5443,7 @@
         <v>17</v>
       </c>
       <c r="K122" t="n">
-        <v>7.009257984692042</v>
+        <v>7.002731373643452</v>
       </c>
     </row>
     <row r="123">
@@ -5484,7 +5484,7 @@
         <v>17</v>
       </c>
       <c r="K123" t="n">
-        <v>7.009257984692042</v>
+        <v>7.002731373643452</v>
       </c>
     </row>
     <row r="124">
@@ -5525,7 +5525,7 @@
         <v>17</v>
       </c>
       <c r="K124" t="n">
-        <v>7.036662400576596</v>
+        <v>7.03448653682228</v>
       </c>
     </row>
     <row r="125">
@@ -5566,7 +5566,7 @@
         <v>17</v>
       </c>
       <c r="K125" t="n">
-        <v>6.995782921034595</v>
+        <v>6.965222870726626</v>
       </c>
     </row>
     <row r="126">
@@ -5607,7 +5607,7 @@
         <v>17</v>
       </c>
       <c r="K126" t="n">
-        <v>6.939650308981772</v>
+        <v>6.948909992854061</v>
       </c>
     </row>
     <row r="127">
@@ -5648,7 +5648,7 @@
         <v>17</v>
       </c>
       <c r="K127" t="n">
-        <v>6.829262396259586</v>
+        <v>6.844761965900958</v>
       </c>
     </row>
     <row r="128">
@@ -5689,7 +5689,7 @@
         <v>17</v>
       </c>
       <c r="K128" t="n">
-        <v>6.829262396259586</v>
+        <v>6.844761965900958</v>
       </c>
     </row>
     <row r="129">
@@ -5730,7 +5730,7 @@
         <v>17</v>
       </c>
       <c r="K129" t="n">
-        <v>6.739686757437209</v>
+        <v>6.759342622864795</v>
       </c>
     </row>
     <row r="130">
@@ -5771,7 +5771,7 @@
         <v>17</v>
       </c>
       <c r="K130" t="n">
-        <v>6.582992726856799</v>
+        <v>6.602081830291315</v>
       </c>
     </row>
     <row r="131">
@@ -5812,7 +5812,7 @@
         <v>17</v>
       </c>
       <c r="K131" t="n">
-        <v>6.427274373633168</v>
+        <v>6.447913261464199</v>
       </c>
     </row>
     <row r="132">
@@ -5853,7 +5853,7 @@
         <v>17</v>
       </c>
       <c r="K132" t="n">
-        <v>6.427274373633168</v>
+        <v>6.447913261464199</v>
       </c>
     </row>
     <row r="133">
@@ -5894,7 +5894,7 @@
         <v>17</v>
       </c>
       <c r="K133" t="n">
-        <v>6.269097881919837</v>
+        <v>6.286437957577838</v>
       </c>
     </row>
     <row r="134">
@@ -5935,7 +5935,7 @@
         <v>17</v>
       </c>
       <c r="K134" t="n">
-        <v>6.164167181636034</v>
+        <v>6.15366395093655</v>
       </c>
     </row>
     <row r="135">
@@ -5976,7 +5976,7 @@
         <v>17</v>
       </c>
       <c r="K135" t="n">
-        <v>6.140849187586153</v>
+        <v>6.15366395093655</v>
       </c>
     </row>
     <row r="136">
@@ -6017,7 +6017,7 @@
         <v>17</v>
       </c>
       <c r="K136" t="n">
-        <v>5.882482856253138</v>
+        <v>5.893461410381708</v>
       </c>
     </row>
     <row r="137">
@@ -6058,7 +6058,7 @@
         <v>17</v>
       </c>
       <c r="K137" t="n">
-        <v>5.736315390548596</v>
+        <v>5.718947930533291</v>
       </c>
     </row>
     <row r="138">
@@ -6099,7 +6099,7 @@
         <v>17</v>
       </c>
       <c r="K138" t="n">
-        <v>5.710260936669161</v>
+        <v>5.712852643823005</v>
       </c>
     </row>
     <row r="139">
@@ -6140,7 +6140,7 @@
         <v>17</v>
       </c>
       <c r="K139" t="n">
-        <v>5.700222144927777</v>
+        <v>5.692598254015039</v>
       </c>
     </row>
     <row r="140">
@@ -6181,7 +6181,7 @@
         <v>17</v>
       </c>
       <c r="K140" t="n">
-        <v>5.711040344275069</v>
+        <v>5.704902857121272</v>
       </c>
     </row>
     <row r="141">
@@ -6222,7 +6222,7 @@
         <v>17</v>
       </c>
       <c r="K141" t="n">
-        <v>6.291535480176309</v>
+        <v>6.26230317497177</v>
       </c>
     </row>
     <row r="142">
@@ -6263,7 +6263,7 @@
         <v>17</v>
       </c>
       <c r="K142" t="n">
-        <v>6.552454352023732</v>
+        <v>6.524154597168152</v>
       </c>
     </row>
     <row r="143">
@@ -6304,7 +6304,7 @@
         <v>17</v>
       </c>
       <c r="K143" t="n">
-        <v>6.763428747104236</v>
+        <v>6.738221031280524</v>
       </c>
     </row>
     <row r="144">
@@ -6345,7 +6345,7 @@
         <v>17</v>
       </c>
       <c r="K144" t="n">
-        <v>6.97259129945409</v>
+        <v>7.105702445742474</v>
       </c>
     </row>
     <row r="145">
@@ -6386,7 +6386,7 @@
         <v>17</v>
       </c>
       <c r="K145" t="n">
-        <v>7.314747643483888</v>
+        <v>7.302580157059705</v>
       </c>
     </row>
     <row r="146">
@@ -6427,7 +6427,7 @@
         <v>17</v>
       </c>
       <c r="K146" t="n">
-        <v>7.402053625346182</v>
+        <v>7.393033836462709</v>
       </c>
     </row>
     <row r="147">
@@ -6468,7 +6468,7 @@
         <v>17</v>
       </c>
       <c r="K147" t="n">
-        <v>7.452460401670667</v>
+        <v>7.45406944170762</v>
       </c>
     </row>
     <row r="148">
@@ -6509,7 +6509,7 @@
         <v>17</v>
       </c>
       <c r="K148" t="n">
-        <v>7.137690582644701</v>
+        <v>7.151236587484997</v>
       </c>
     </row>
     <row r="149">
@@ -6550,7 +6550,7 @@
         <v>17</v>
       </c>
       <c r="K149" t="n">
-        <v>7.060329402812143</v>
+        <v>7.073587254435585</v>
       </c>
     </row>
     <row r="150">
@@ -6591,7 +6591,7 @@
         <v>17</v>
       </c>
       <c r="K150" t="n">
-        <v>7.060329402812143</v>
+        <v>7.073587254435585</v>
       </c>
     </row>
     <row r="151">
@@ -6632,7 +6632,7 @@
         <v>17</v>
       </c>
       <c r="K151" t="n">
-        <v>7.040948934445939</v>
+        <v>6.989288158253655</v>
       </c>
     </row>
     <row r="152">
@@ -6673,7 +6673,7 @@
         <v>17</v>
       </c>
       <c r="K152" t="n">
-        <v>6.715020032112586</v>
+        <v>6.63956582671167</v>
       </c>
     </row>
     <row r="153">
@@ -6714,7 +6714,7 @@
         <v>17</v>
       </c>
       <c r="K153" t="n">
-        <v>6.338791090776827</v>
+        <v>6.363712727227157</v>
       </c>
     </row>
     <row r="154">
@@ -6755,7 +6755,7 @@
         <v>17</v>
       </c>
       <c r="K154" t="n">
-        <v>6.178996684265116</v>
+        <v>6.206880308422047</v>
       </c>
     </row>
     <row r="155">
@@ -6796,7 +6796,7 @@
         <v>17</v>
       </c>
       <c r="K155" t="n">
-        <v>6.000334894592796</v>
+        <v>6.031544329445902</v>
       </c>
     </row>
     <row r="156">
@@ -6837,7 +6837,7 @@
         <v>17</v>
       </c>
       <c r="K156" t="n">
-        <v>5.329949029981647</v>
+        <v>5.350677701696725</v>
       </c>
     </row>
     <row r="157">
@@ -6878,7 +6878,7 @@
         <v>17</v>
       </c>
       <c r="K157" t="n">
-        <v>5.192684241831878</v>
+        <v>5.203348639064105</v>
       </c>
     </row>
     <row r="158">
@@ -6919,7 +6919,7 @@
         <v>17</v>
       </c>
       <c r="K158" t="n">
-        <v>5.034796515651481</v>
+        <v>5.042390611054621</v>
       </c>
     </row>
     <row r="159">
@@ -6960,7 +6960,7 @@
         <v>17</v>
       </c>
       <c r="K159" t="n">
-        <v>5.156053736591606</v>
+        <v>5.136348955563021</v>
       </c>
     </row>
     <row r="160">
@@ -7001,7 +7001,7 @@
         <v>17</v>
       </c>
       <c r="K160" t="n">
-        <v>5.57742993932842</v>
+        <v>5.55144672363453</v>
       </c>
     </row>
     <row r="161">
@@ -7042,7 +7042,7 @@
         <v>17</v>
       </c>
       <c r="K161" t="n">
-        <v>5.747734269282226</v>
+        <v>5.776322621998234</v>
       </c>
     </row>
     <row r="162">
@@ -7083,7 +7083,7 @@
         <v>17</v>
       </c>
       <c r="K162" t="n">
-        <v>6.261073493671605</v>
+        <v>6.248919972144285</v>
       </c>
     </row>
     <row r="163">
@@ -7124,7 +7124,7 @@
         <v>17</v>
       </c>
       <c r="K163" t="n">
-        <v>6.3509692844717</v>
+        <v>6.344427982629672</v>
       </c>
     </row>
     <row r="164">
@@ -7165,7 +7165,7 @@
         <v>17</v>
       </c>
       <c r="K164" t="n">
-        <v>6.426002307031754</v>
+        <v>6.43150528916774</v>
       </c>
     </row>
     <row r="165">
@@ -7206,7 +7206,7 @@
         <v>17</v>
       </c>
       <c r="K165" t="n">
-        <v>6.493814413278744</v>
+        <v>6.498408830801671</v>
       </c>
     </row>
     <row r="166">
@@ -7247,7 +7247,7 @@
         <v>17</v>
       </c>
       <c r="K166" t="n">
-        <v>6.493814413278744</v>
+        <v>6.498408830801671</v>
       </c>
     </row>
     <row r="167">
@@ -7288,7 +7288,7 @@
         <v>17</v>
       </c>
       <c r="K167" t="n">
-        <v>6.484449522851524</v>
+        <v>6.490944130896361</v>
       </c>
     </row>
     <row r="168">
@@ -7329,7 +7329,7 @@
         <v>17</v>
       </c>
       <c r="K168" t="n">
-        <v>6.296829148845255</v>
+        <v>6.30590760246487</v>
       </c>
     </row>
     <row r="169">
@@ -7370,7 +7370,7 @@
         <v>17</v>
       </c>
       <c r="K169" t="n">
-        <v>6.296829148845255</v>
+        <v>6.30590760246487</v>
       </c>
     </row>
     <row r="170">
@@ -7411,7 +7411,7 @@
         <v>17</v>
       </c>
       <c r="K170" t="n">
-        <v>6.252126694619706</v>
+        <v>6.243775251025913</v>
       </c>
     </row>
     <row r="171">
@@ -7452,7 +7452,7 @@
         <v>17</v>
       </c>
       <c r="K171" t="n">
-        <v>6.158763854286831</v>
+        <v>6.168429468307566</v>
       </c>
     </row>
     <row r="172">
@@ -7493,7 +7493,7 @@
         <v>17</v>
       </c>
       <c r="K172" t="n">
-        <v>6.096264577712642</v>
+        <v>6.084313006567648</v>
       </c>
     </row>
     <row r="173">
@@ -7534,7 +7534,7 @@
         <v>17</v>
       </c>
       <c r="K173" t="n">
-        <v>6.018298821252825</v>
+        <v>6.032455212563289</v>
       </c>
     </row>
     <row r="174">
@@ -7575,7 +7575,7 @@
         <v>17</v>
       </c>
       <c r="K174" t="n">
-        <v>5.80423300936083</v>
+        <v>5.824560652973466</v>
       </c>
     </row>
     <row r="175">
@@ -7616,7 +7616,7 @@
         <v>17</v>
       </c>
       <c r="K175" t="n">
-        <v>5.80423300936083</v>
+        <v>5.783411711045866</v>
       </c>
     </row>
     <row r="176">
@@ -7657,7 +7657,7 @@
         <v>17</v>
       </c>
       <c r="K176" t="n">
-        <v>5.770125749880156</v>
+        <v>5.783411711045866</v>
       </c>
     </row>
     <row r="177">
@@ -7698,7 +7698,7 @@
         <v>17</v>
       </c>
       <c r="K177" t="n">
-        <v>5.246029265980684</v>
+        <v>5.273689208370009</v>
       </c>
     </row>
     <row r="178">
@@ -7739,7 +7739,7 @@
         <v>17</v>
       </c>
       <c r="K178" t="n">
-        <v>5.246029265980684</v>
+        <v>5.217788954896063</v>
       </c>
     </row>
     <row r="179">
@@ -7780,7 +7780,7 @@
         <v>17</v>
       </c>
       <c r="K179" t="n">
-        <v>4.912754819939559</v>
+        <v>4.883659247979038</v>
       </c>
     </row>
     <row r="180">
@@ -7821,7 +7821,7 @@
         <v>17</v>
       </c>
       <c r="K180" t="n">
-        <v>4.866380783143212</v>
+        <v>4.784665552852319</v>
       </c>
     </row>
     <row r="181">
@@ -7862,7 +7862,7 @@
         <v>17</v>
       </c>
       <c r="K181" t="n">
-        <v>4.626524534169275</v>
+        <v>4.631261157514952</v>
       </c>
     </row>
     <row r="182">
@@ -7903,7 +7903,7 @@
         <v>17</v>
       </c>
       <c r="K182" t="n">
-        <v>4.626524534169275</v>
+        <v>4.631261157514952</v>
       </c>
     </row>
     <row r="183">
@@ -7944,7 +7944,7 @@
         <v>17</v>
       </c>
       <c r="K183" t="n">
-        <v>4.680974129789471</v>
+        <v>4.672467824556563</v>
       </c>
     </row>
     <row r="184">
@@ -7985,7 +7985,7 @@
         <v>17</v>
       </c>
       <c r="K184" t="n">
-        <v>4.697421348352245</v>
+        <v>4.691065899382967</v>
       </c>
     </row>
     <row r="185">
@@ -8026,7 +8026,7 @@
         <v>17</v>
       </c>
       <c r="K185" t="n">
-        <v>4.970390325833943</v>
+        <v>4.959985830152203</v>
       </c>
     </row>
     <row r="186">
@@ -8067,7 +8067,7 @@
         <v>17</v>
       </c>
       <c r="K186" t="n">
-        <v>5.042033068436351</v>
+        <v>5.061964276895472</v>
       </c>
     </row>
     <row r="187">
@@ -8108,7 +8108,7 @@
         <v>17</v>
       </c>
       <c r="K187" t="n">
-        <v>5.144273510192376</v>
+        <v>5.139621947657399</v>
       </c>
     </row>
     <row r="188">
@@ -8149,7 +8149,7 @@
         <v>17</v>
       </c>
       <c r="K188" t="n">
-        <v>5.151181089022467</v>
+        <v>5.155013385865095</v>
       </c>
     </row>
     <row r="189">
@@ -8190,7 +8190,7 @@
         <v>17</v>
       </c>
       <c r="K189" t="n">
-        <v>5.127630386390929</v>
+        <v>5.131134106491538</v>
       </c>
     </row>
     <row r="190">
@@ -8231,7 +8231,7 @@
         <v>17</v>
       </c>
       <c r="K190" t="n">
-        <v>5.123446376741982</v>
+        <v>5.124655550525722</v>
       </c>
     </row>
     <row r="191">
@@ -8272,7 +8272,7 @@
         <v>17</v>
       </c>
       <c r="K191" t="n">
-        <v>5.126603929821988</v>
+        <v>5.134248956556644</v>
       </c>
     </row>
     <row r="192">
@@ -8313,7 +8313,7 @@
         <v>17</v>
       </c>
       <c r="K192" t="n">
-        <v>5.139644963111619</v>
+        <v>5.139100160208838</v>
       </c>
     </row>
     <row r="193">
@@ -8354,7 +8354,7 @@
         <v>17</v>
       </c>
       <c r="K193" t="n">
-        <v>5.139131518439145</v>
+        <v>5.13581627233214</v>
       </c>
     </row>
     <row r="194">
@@ -8395,7 +8395,7 @@
         <v>17</v>
       </c>
       <c r="K194" t="n">
-        <v>5.133982178218036</v>
+        <v>5.13581627233214</v>
       </c>
     </row>
     <row r="195">
@@ -8436,7 +8436,7 @@
         <v>17</v>
       </c>
       <c r="K195" t="n">
-        <v>5.121538876501863</v>
+        <v>5.117998934186575</v>
       </c>
     </row>
     <row r="196">
@@ -8477,7 +8477,7 @@
         <v>17</v>
       </c>
       <c r="K196" t="n">
-        <v>5.087714003405997</v>
+        <v>5.090020584402274</v>
       </c>
     </row>
     <row r="197">
@@ -8518,7 +8518,7 @@
         <v>17</v>
       </c>
       <c r="K197" t="n">
-        <v>5.068168270738139</v>
+        <v>5.065475118317499</v>
       </c>
     </row>
     <row r="198">
@@ -8559,7 +8559,7 @@
         <v>17</v>
       </c>
       <c r="K198" t="n">
-        <v>5.08878105473769</v>
+        <v>5.095656792811958</v>
       </c>
     </row>
     <row r="199">
@@ -8600,7 +8600,7 @@
         <v>17</v>
       </c>
       <c r="K199" t="n">
-        <v>5.115815920964135</v>
+        <v>5.111366260963839</v>
       </c>
     </row>
     <row r="200">
@@ -8641,7 +8641,7 @@
         <v>17</v>
       </c>
       <c r="K200" t="n">
-        <v>5.184305404881255</v>
+        <v>5.181655880515361</v>
       </c>
     </row>
     <row r="201">
@@ -8682,7 +8682,7 @@
         <v>17</v>
       </c>
       <c r="K201" t="n">
-        <v>5.188662911721403</v>
+        <v>5.180902690524934</v>
       </c>
     </row>
     <row r="202">
@@ -8723,7 +8723,7 @@
         <v>17</v>
       </c>
       <c r="K202" t="n">
-        <v>5.282291494160479</v>
+        <v>5.297215214334836</v>
       </c>
     </row>
     <row r="203">
@@ -8764,7 +8764,7 @@
         <v>17</v>
       </c>
       <c r="K203" t="n">
-        <v>5.300511370542866</v>
+        <v>5.297215214334836</v>
       </c>
     </row>
     <row r="204">
@@ -8805,7 +8805,7 @@
         <v>17</v>
       </c>
       <c r="K204" t="n">
-        <v>5.306780504641036</v>
+        <v>5.305149569350647</v>
       </c>
     </row>
     <row r="205">
@@ -8846,7 +8846,7 @@
         <v>17</v>
       </c>
       <c r="K205" t="n">
-        <v>5.299836384077633</v>
+        <v>5.299900413890381</v>
       </c>
     </row>
     <row r="206">
@@ -8887,7 +8887,7 @@
         <v>17</v>
       </c>
       <c r="K206" t="n">
-        <v>5.265229432269085</v>
+        <v>5.268872319911711</v>
       </c>
     </row>
     <row r="207">
@@ -8928,7 +8928,7 @@
         <v>17</v>
       </c>
       <c r="K207" t="n">
-        <v>5.091365307069992</v>
+        <v>5.100065697461008</v>
       </c>
     </row>
     <row r="208">
@@ -8969,7 +8969,7 @@
         <v>17</v>
       </c>
       <c r="K208" t="n">
-        <v>5.091365307069992</v>
+        <v>5.100065697461008</v>
       </c>
     </row>
     <row r="209">
@@ -9010,7 +9010,7 @@
         <v>17</v>
       </c>
       <c r="K209" t="n">
-        <v>4.862482790413713</v>
+        <v>4.873182265775307</v>
       </c>
     </row>
     <row r="210">
@@ -9051,7 +9051,7 @@
         <v>17</v>
       </c>
       <c r="K210" t="n">
-        <v>4.838982019579614</v>
+        <v>4.836369403739383</v>
       </c>
     </row>
     <row r="211">
@@ -9092,7 +9092,7 @@
         <v>17</v>
       </c>
       <c r="K211" t="n">
-        <v>4.869418055800006</v>
+        <v>4.863411672434975</v>
       </c>
     </row>
     <row r="212">
@@ -9133,7 +9133,7 @@
         <v>17</v>
       </c>
       <c r="K212" t="n">
-        <v>5.057276074725584</v>
+        <v>5.045608690763564</v>
       </c>
     </row>
     <row r="213">
@@ -9174,7 +9174,7 @@
         <v>17</v>
       </c>
       <c r="K213" t="n">
-        <v>5.299347530802288</v>
+        <v>5.286833718245051</v>
       </c>
     </row>
     <row r="214">
@@ -9215,7 +9215,7 @@
         <v>17</v>
       </c>
       <c r="K214" t="n">
-        <v>5.587741299700951</v>
+        <v>5.570931232146719</v>
       </c>
     </row>
     <row r="215">
@@ -9256,7 +9256,7 @@
         <v>17</v>
       </c>
       <c r="K215" t="n">
-        <v>5.788115429514686</v>
+        <v>5.76345046535116</v>
       </c>
     </row>
     <row r="216">
@@ -9297,7 +9297,7 @@
         <v>17</v>
       </c>
       <c r="K216" t="n">
-        <v>5.788115429514686</v>
+        <v>5.76345046535116</v>
       </c>
     </row>
     <row r="217">
@@ -9338,7 +9338,7 @@
         <v>17</v>
       </c>
       <c r="K217" t="n">
-        <v>6.075201464833206</v>
+        <v>6.048709644940418</v>
       </c>
     </row>
     <row r="218">
@@ -9379,7 +9379,7 @@
         <v>17</v>
       </c>
       <c r="K218" t="n">
-        <v>6.329550934338049</v>
+        <v>6.306191041694616</v>
       </c>
     </row>
     <row r="219">
@@ -9420,7 +9420,7 @@
         <v>17</v>
       </c>
       <c r="K219" t="n">
-        <v>7.09805759673106</v>
+        <v>7.045686325133969</v>
       </c>
     </row>
     <row r="220">
@@ -9461,7 +9461,7 @@
         <v>17</v>
       </c>
       <c r="K220" t="n">
-        <v>7.713915197313159</v>
+        <v>7.639524494156501</v>
       </c>
     </row>
     <row r="221">
@@ -9502,7 +9502,7 @@
         <v>17</v>
       </c>
       <c r="K221" t="n">
-        <v>8.310256181772115</v>
+        <v>8.269080203468771</v>
       </c>
     </row>
     <row r="222">
@@ -9543,7 +9543,7 @@
         <v>17</v>
       </c>
       <c r="K222" t="n">
-        <v>8.310256181772115</v>
+        <v>8.269080203468771</v>
       </c>
     </row>
     <row r="223">
@@ -9584,7 +9584,7 @@
         <v>17</v>
       </c>
       <c r="K223" t="n">
-        <v>8.705703360451546</v>
+        <v>8.672539451998677</v>
       </c>
     </row>
     <row r="224">
@@ -9625,7 +9625,7 @@
         <v>17</v>
       </c>
       <c r="K224" t="n">
-        <v>8.705703360451546</v>
+        <v>8.672539451998677</v>
       </c>
     </row>
     <row r="225">
@@ -9666,7 +9666,7 @@
         <v>17</v>
       </c>
       <c r="K225" t="n">
-        <v>8.705703360451546</v>
+        <v>8.672539451998677</v>
       </c>
     </row>
     <row r="226">
@@ -9707,7 +9707,7 @@
         <v>17</v>
       </c>
       <c r="K226" t="n">
-        <v>9.481929897370215</v>
+        <v>9.439958811882898</v>
       </c>
     </row>
     <row r="227">
@@ -9748,7 +9748,7 @@
         <v>17</v>
       </c>
       <c r="K227" t="n">
-        <v>10.31211440452167</v>
+        <v>10.71892796676812</v>
       </c>
     </row>
     <row r="228">
@@ -9789,7 +9789,7 @@
         <v>17</v>
       </c>
       <c r="K228" t="n">
-        <v>12.23858890723223</v>
+        <v>12.19396779017492</v>
       </c>
     </row>
     <row r="229">
@@ -9830,7 +9830,7 @@
         <v>17</v>
       </c>
       <c r="K229" t="n">
-        <v>12.85838431411921</v>
+        <v>13.31269203496238</v>
       </c>
     </row>
     <row r="230">
@@ -9871,7 +9871,7 @@
         <v>17</v>
       </c>
       <c r="K230" t="n">
-        <v>12.85838431411921</v>
+        <v>13.31269203496238</v>
       </c>
     </row>
     <row r="231">
@@ -9912,7 +9912,7 @@
         <v>17</v>
       </c>
       <c r="K231" t="n">
-        <v>13.72142780202636</v>
+        <v>13.71618450517966</v>
       </c>
     </row>
     <row r="232">
@@ -9953,7 +9953,7 @@
         <v>19</v>
       </c>
       <c r="K232" t="n">
-        <v>1.75240180194189</v>
+        <v>1.761619037047926</v>
       </c>
     </row>
     <row r="233">
@@ -9994,7 +9994,7 @@
         <v>19</v>
       </c>
       <c r="K233" t="n">
-        <v>1.789156886112483</v>
+        <v>1.782313828613929</v>
       </c>
     </row>
     <row r="234">
@@ -10035,7 +10035,7 @@
         <v>19</v>
       </c>
       <c r="K234" t="n">
-        <v>1.927272588216745</v>
+        <v>1.919983378203505</v>
       </c>
     </row>
     <row r="235">
@@ -10076,7 +10076,7 @@
         <v>19</v>
       </c>
       <c r="K235" t="n">
-        <v>2.14817911006942</v>
+        <v>2.256167519833057</v>
       </c>
     </row>
     <row r="236">
@@ -10117,7 +10117,7 @@
         <v>19</v>
       </c>
       <c r="K236" t="n">
-        <v>2.267337292229854</v>
+        <v>2.256167519833057</v>
       </c>
     </row>
     <row r="237">
@@ -10158,7 +10158,7 @@
         <v>19</v>
       </c>
       <c r="K237" t="n">
-        <v>2.501729729984032</v>
+        <v>2.491611291929246</v>
       </c>
     </row>
     <row r="238">
@@ -10199,7 +10199,7 @@
         <v>19</v>
       </c>
       <c r="K238" t="n">
-        <v>2.594761882185537</v>
+        <v>2.588380022636111</v>
       </c>
     </row>
     <row r="239">
@@ -10240,7 +10240,7 @@
         <v>19</v>
       </c>
       <c r="K239" t="n">
-        <v>2.731870341973139</v>
+        <v>2.728853865887447</v>
       </c>
     </row>
     <row r="240">
@@ -10281,7 +10281,7 @@
         <v>19</v>
       </c>
       <c r="K240" t="n">
-        <v>2.792800012291472</v>
+        <v>2.788205691254029</v>
       </c>
     </row>
     <row r="241">
@@ -10322,7 +10322,7 @@
         <v>19</v>
       </c>
       <c r="K241" t="n">
-        <v>2.792800012291472</v>
+        <v>2.788205691254029</v>
       </c>
     </row>
     <row r="242">
@@ -10363,7 +10363,7 @@
         <v>19</v>
       </c>
       <c r="K242" t="n">
-        <v>2.792800012291472</v>
+        <v>2.788205691254029</v>
       </c>
     </row>
     <row r="243">
@@ -10404,7 +10404,7 @@
         <v>19</v>
       </c>
       <c r="K243" t="n">
-        <v>2.741824170702985</v>
+        <v>2.745029898031879</v>
       </c>
     </row>
     <row r="244">
@@ -10445,7 +10445,7 @@
         <v>19</v>
       </c>
       <c r="K244" t="n">
-        <v>2.741824170702985</v>
+        <v>2.745029898031879</v>
       </c>
     </row>
     <row r="245">
@@ -10486,7 +10486,7 @@
         <v>19</v>
       </c>
       <c r="K245" t="n">
-        <v>2.664648918063546</v>
+        <v>2.670407213359229</v>
       </c>
     </row>
     <row r="246">
@@ -10527,7 +10527,7 @@
         <v>19</v>
       </c>
       <c r="K246" t="n">
-        <v>2.569501553993635</v>
+        <v>2.577364383916254</v>
       </c>
     </row>
     <row r="247">
@@ -10568,7 +10568,7 @@
         <v>19</v>
       </c>
       <c r="K247" t="n">
-        <v>2.569501553993635</v>
+        <v>2.577364383916254</v>
       </c>
     </row>
     <row r="248">
@@ -10609,7 +10609,7 @@
         <v>19</v>
       </c>
       <c r="K248" t="n">
-        <v>2.446805947169418</v>
+        <v>2.456914843267194</v>
       </c>
     </row>
     <row r="249">
@@ -10650,7 +10650,7 @@
         <v>19</v>
       </c>
       <c r="K249" t="n">
-        <v>2.321903925322439</v>
+        <v>2.332338944607041</v>
       </c>
     </row>
     <row r="250">
@@ -10691,7 +10691,7 @@
         <v>19</v>
       </c>
       <c r="K250" t="n">
-        <v>2.321903925322439</v>
+        <v>2.332338944607041</v>
       </c>
     </row>
     <row r="251">
@@ -10732,7 +10732,7 @@
         <v>19</v>
       </c>
       <c r="K251" t="n">
-        <v>2.190955436752826</v>
+        <v>2.071831111792786</v>
       </c>
     </row>
     <row r="252">
@@ -10773,7 +10773,7 @@
         <v>19</v>
       </c>
       <c r="K252" t="n">
-        <v>1.871356496356105</v>
+        <v>1.877638927346549</v>
       </c>
     </row>
     <row r="253">
@@ -10814,7 +10814,7 @@
         <v>19</v>
       </c>
       <c r="K253" t="n">
-        <v>1.689331763094933</v>
+        <v>1.691875258394973</v>
       </c>
     </row>
     <row r="254">
@@ -10855,7 +10855,7 @@
         <v>19</v>
       </c>
       <c r="K254" t="n">
-        <v>1.643611831257944</v>
+        <v>1.644265817586015</v>
       </c>
     </row>
     <row r="255">
@@ -10896,7 +10896,7 @@
         <v>19</v>
       </c>
       <c r="K255" t="n">
-        <v>1.665130308081097</v>
+        <v>1.662506535975598</v>
       </c>
     </row>
     <row r="256">
@@ -10937,7 +10937,7 @@
         <v>19</v>
       </c>
       <c r="K256" t="n">
-        <v>1.694159118059502</v>
+        <v>1.692209229124068</v>
       </c>
     </row>
     <row r="257">
@@ -10978,7 +10978,7 @@
         <v>19</v>
       </c>
       <c r="K257" t="n">
-        <v>1.694702867547865</v>
+        <v>1.690660722717455</v>
       </c>
     </row>
     <row r="258">
@@ -11019,7 +11019,7 @@
         <v>19</v>
       </c>
       <c r="K258" t="n">
-        <v>1.737120644926202</v>
+        <v>1.735455762065908</v>
       </c>
     </row>
     <row r="259">
@@ -11060,7 +11060,7 @@
         <v>19</v>
       </c>
       <c r="K259" t="n">
-        <v>1.737120644926202</v>
+        <v>1.735455762065908</v>
       </c>
     </row>
     <row r="260">
@@ -11101,7 +11101,7 @@
         <v>19</v>
       </c>
       <c r="K260" t="n">
-        <v>1.737120644926202</v>
+        <v>1.735455762065908</v>
       </c>
     </row>
     <row r="261">
@@ -11142,7 +11142,7 @@
         <v>19</v>
       </c>
       <c r="K261" t="n">
-        <v>1.737120644926202</v>
+        <v>1.735455762065908</v>
       </c>
     </row>
     <row r="262">
@@ -11183,7 +11183,7 @@
         <v>19</v>
       </c>
       <c r="K262" t="n">
-        <v>1.737120644926202</v>
+        <v>1.75917900783314</v>
       </c>
     </row>
     <row r="263">
@@ -11224,7 +11224,7 @@
         <v>19</v>
       </c>
       <c r="K263" t="n">
-        <v>2.018537668015982</v>
+        <v>2.013541050495229</v>
       </c>
     </row>
     <row r="264">
@@ -11265,7 +11265,7 @@
         <v>19</v>
       </c>
       <c r="K264" t="n">
-        <v>2.170678739802113</v>
+        <v>2.165101994855239</v>
       </c>
     </row>
     <row r="265">
@@ -11306,7 +11306,7 @@
         <v>19</v>
       </c>
       <c r="K265" t="n">
-        <v>2.246060906303259</v>
+        <v>2.241343398494508</v>
       </c>
     </row>
     <row r="266">
@@ -11347,7 +11347,7 @@
         <v>19</v>
       </c>
       <c r="K266" t="n">
-        <v>2.312094571570058</v>
+        <v>2.307938011356025</v>
       </c>
     </row>
     <row r="267">
@@ -11388,7 +11388,7 @@
         <v>19</v>
       </c>
       <c r="K267" t="n">
-        <v>2.364082991661326</v>
+        <v>2.361044357950932</v>
       </c>
     </row>
     <row r="268">
@@ -11429,7 +11429,7 @@
         <v>19</v>
       </c>
       <c r="K268" t="n">
-        <v>2.364082991661326</v>
+        <v>2.361044357950932</v>
       </c>
     </row>
     <row r="269">
@@ -11470,7 +11470,7 @@
         <v>19</v>
       </c>
       <c r="K269" t="n">
-        <v>2.475022034916729</v>
+        <v>2.473888764911384</v>
       </c>
     </row>
     <row r="270">
@@ -11511,7 +11511,7 @@
         <v>19</v>
       </c>
       <c r="K270" t="n">
-        <v>2.509627822504262</v>
+        <v>2.504252392849067</v>
       </c>
     </row>
     <row r="271">
@@ -11552,7 +11552,7 @@
         <v>19</v>
       </c>
       <c r="K271" t="n">
-        <v>2.595429063582091</v>
+        <v>2.589847413715654</v>
       </c>
     </row>
     <row r="272">
@@ -11593,7 +11593,7 @@
         <v>19</v>
       </c>
       <c r="K272" t="n">
-        <v>2.667042020659017</v>
+        <v>2.663037467636403</v>
       </c>
     </row>
     <row r="273">
@@ -11634,7 +11634,7 @@
         <v>19</v>
       </c>
       <c r="K273" t="n">
-        <v>2.717860119206158</v>
+        <v>2.71497404888639</v>
       </c>
     </row>
     <row r="274">
@@ -11675,7 +11675,7 @@
         <v>19</v>
       </c>
       <c r="K274" t="n">
-        <v>2.717860119206158</v>
+        <v>2.71497404888639</v>
       </c>
     </row>
     <row r="275">
@@ -11716,7 +11716,7 @@
         <v>19</v>
       </c>
       <c r="K275" t="n">
-        <v>2.862571971658902</v>
+        <v>2.859561081788025</v>
       </c>
     </row>
     <row r="276">
@@ -11757,7 +11757,7 @@
         <v>19</v>
       </c>
       <c r="K276" t="n">
-        <v>2.889561366611723</v>
+        <v>2.890880330137259</v>
       </c>
     </row>
     <row r="277">
@@ -11798,7 +11798,7 @@
         <v>19</v>
       </c>
       <c r="K277" t="n">
-        <v>2.889561366611723</v>
+        <v>2.890880330137259</v>
       </c>
     </row>
     <row r="278">
@@ -11839,7 +11839,7 @@
         <v>19</v>
       </c>
       <c r="K278" t="n">
-        <v>2.788479967912038</v>
+        <v>2.789700357105817</v>
       </c>
     </row>
     <row r="279">
@@ -11880,7 +11880,7 @@
         <v>19</v>
       </c>
       <c r="K279" t="n">
-        <v>2.788479967912038</v>
+        <v>2.789700357105817</v>
       </c>
     </row>
     <row r="280">
@@ -11921,7 +11921,7 @@
         <v>19</v>
       </c>
       <c r="K280" t="n">
-        <v>2.691333763469939</v>
+        <v>2.694227796920716</v>
       </c>
     </row>
     <row r="281">
@@ -11962,7 +11962,7 @@
         <v>19</v>
       </c>
       <c r="K281" t="n">
-        <v>2.630226475238568</v>
+        <v>2.635163329588112</v>
       </c>
     </row>
     <row r="282">
@@ -12003,7 +12003,7 @@
         <v>19</v>
       </c>
       <c r="K282" t="n">
-        <v>2.542464838594832</v>
+        <v>2.548560258881797</v>
       </c>
     </row>
     <row r="283">
@@ -12044,7 +12044,7 @@
         <v>19</v>
       </c>
       <c r="K283" t="n">
-        <v>2.443517415461807</v>
+        <v>2.449762128705601</v>
       </c>
     </row>
     <row r="284">
@@ -12085,7 +12085,7 @@
         <v>19</v>
       </c>
       <c r="K284" t="n">
-        <v>2.321978711167837</v>
+        <v>2.322834047649811</v>
       </c>
     </row>
     <row r="285">
@@ -12126,7 +12126,7 @@
         <v>19</v>
       </c>
       <c r="K285" t="n">
-        <v>2.321978711167837</v>
+        <v>2.322834047649811</v>
       </c>
     </row>
     <row r="286">
@@ -12167,7 +12167,7 @@
         <v>19</v>
       </c>
       <c r="K286" t="n">
-        <v>2.321978711167837</v>
+        <v>2.322834047649811</v>
       </c>
     </row>
     <row r="287">
@@ -12208,7 +12208,7 @@
         <v>19</v>
       </c>
       <c r="K287" t="n">
-        <v>2.24708529962274</v>
+        <v>2.177201072036584</v>
       </c>
     </row>
     <row r="288">
@@ -12249,7 +12249,7 @@
         <v>19</v>
       </c>
       <c r="K288" t="n">
-        <v>2.171746408906799</v>
+        <v>2.177201072036584</v>
       </c>
     </row>
     <row r="289">
@@ -12290,7 +12290,7 @@
         <v>19</v>
       </c>
       <c r="K289" t="n">
-        <v>1.973920028654504</v>
+        <v>1.975366620185895</v>
       </c>
     </row>
     <row r="290">
@@ -12331,7 +12331,7 @@
         <v>19</v>
       </c>
       <c r="K290" t="n">
-        <v>1.973920028654504</v>
+        <v>1.975366620185895</v>
       </c>
     </row>
     <row r="291">
@@ -12372,7 +12372,7 @@
         <v>19</v>
       </c>
       <c r="K291" t="n">
-        <v>2.109647533148084</v>
+        <v>2.106256661783527</v>
       </c>
     </row>
     <row r="292">
@@ -12413,7 +12413,7 @@
         <v>19</v>
       </c>
       <c r="K292" t="n">
-        <v>2.167456601091663</v>
+        <v>2.163815252016861</v>
       </c>
     </row>
     <row r="293">
@@ -12454,7 +12454,7 @@
         <v>19</v>
       </c>
       <c r="K293" t="n">
-        <v>2.22752158690021</v>
+        <v>2.224039249079345</v>
       </c>
     </row>
     <row r="294">
@@ -12495,7 +12495,7 @@
         <v>19</v>
       </c>
       <c r="K294" t="n">
-        <v>2.22752158690021</v>
+        <v>2.224039249079345</v>
       </c>
     </row>
     <row r="295">
@@ -12536,7 +12536,7 @@
         <v>19</v>
       </c>
       <c r="K295" t="n">
-        <v>2.421277748022336</v>
+        <v>2.418728888225798</v>
       </c>
     </row>
     <row r="296">
@@ -12577,7 +12577,7 @@
         <v>19</v>
       </c>
       <c r="K296" t="n">
-        <v>2.440420117935278</v>
+        <v>2.39361340672585</v>
       </c>
     </row>
     <row r="297">
@@ -12618,7 +12618,7 @@
         <v>19</v>
       </c>
       <c r="K297" t="n">
-        <v>2.285979719057656</v>
+        <v>2.292644073383602</v>
       </c>
     </row>
     <row r="298">
@@ -12659,7 +12659,7 @@
         <v>19</v>
       </c>
       <c r="K298" t="n">
-        <v>2.037211509055557</v>
+        <v>2.043445700763973</v>
       </c>
     </row>
     <row r="299">
@@ -12700,7 +12700,7 @@
         <v>19</v>
       </c>
       <c r="K299" t="n">
-        <v>1.889675224490126</v>
+        <v>1.893488177280682</v>
       </c>
     </row>
     <row r="300">
@@ -12741,7 +12741,7 @@
         <v>19</v>
       </c>
       <c r="K300" t="n">
-        <v>1.759458843623075</v>
+        <v>1.761840861748246</v>
       </c>
     </row>
     <row r="301">
@@ -12782,7 +12782,7 @@
         <v>19</v>
       </c>
       <c r="K301" t="n">
-        <v>1.77134681957331</v>
+        <v>1.770642443177784</v>
       </c>
     </row>
     <row r="302">
@@ -12823,7 +12823,7 @@
         <v>19</v>
       </c>
       <c r="K302" t="n">
-        <v>1.77134681957331</v>
+        <v>1.783789919343378</v>
       </c>
     </row>
     <row r="303">
@@ -12864,7 +12864,7 @@
         <v>19</v>
       </c>
       <c r="K303" t="n">
-        <v>1.801506841187101</v>
+        <v>1.800674967006299</v>
       </c>
     </row>
     <row r="304">
@@ -12905,7 +12905,7 @@
         <v>19</v>
       </c>
       <c r="K304" t="n">
-        <v>1.803761174008027</v>
+        <v>1.804366478655874</v>
       </c>
     </row>
     <row r="305">
@@ -12946,7 +12946,7 @@
         <v>19</v>
       </c>
       <c r="K305" t="n">
-        <v>1.79488214087712</v>
+        <v>1.794881650078996</v>
       </c>
     </row>
     <row r="306">
@@ -12987,7 +12987,7 @@
         <v>19</v>
       </c>
       <c r="K306" t="n">
-        <v>1.848270267471769</v>
+        <v>1.846390704960421</v>
       </c>
     </row>
     <row r="307">
@@ -13028,7 +13028,7 @@
         <v>19</v>
       </c>
       <c r="K307" t="n">
-        <v>1.872727157886485</v>
+        <v>1.871859581235214</v>
       </c>
     </row>
     <row r="308">
@@ -13069,7 +13069,7 @@
         <v>19</v>
       </c>
       <c r="K308" t="n">
-        <v>1.92098982920699</v>
+        <v>1.942373424568298</v>
       </c>
     </row>
     <row r="309">
@@ -13110,7 +13110,7 @@
         <v>19</v>
       </c>
       <c r="K309" t="n">
-        <v>1.941786022699924</v>
+        <v>1.942373424568298</v>
       </c>
     </row>
     <row r="310">
@@ -13151,7 +13151,7 @@
         <v>19</v>
       </c>
       <c r="K310" t="n">
-        <v>1.752799431927451</v>
+        <v>1.760237963451229</v>
       </c>
     </row>
     <row r="311">
@@ -13192,7 +13192,7 @@
         <v>19</v>
       </c>
       <c r="K311" t="n">
-        <v>1.625373886642538</v>
+        <v>1.632607256527796</v>
       </c>
     </row>
     <row r="312">
@@ -13233,7 +13233,7 @@
         <v>19</v>
       </c>
       <c r="K312" t="n">
-        <v>1.625373886642538</v>
+        <v>1.632607256527796</v>
       </c>
     </row>
     <row r="313">
@@ -13274,7 +13274,7 @@
         <v>19</v>
       </c>
       <c r="K313" t="n">
-        <v>1.625373886642538</v>
+        <v>1.632607256527796</v>
       </c>
     </row>
     <row r="314">
@@ -13315,7 +13315,7 @@
         <v>19</v>
       </c>
       <c r="K314" t="n">
-        <v>1.520358284837885</v>
+        <v>1.523395504380308</v>
       </c>
     </row>
     <row r="315">
@@ -13356,7 +13356,7 @@
         <v>19</v>
       </c>
       <c r="K315" t="n">
-        <v>1.494355564426814</v>
+        <v>1.497514353975563</v>
       </c>
     </row>
     <row r="316">
@@ -13397,7 +13397,7 @@
         <v>19</v>
       </c>
       <c r="K316" t="n">
-        <v>1.579628941434417</v>
+        <v>1.576364890259819</v>
       </c>
     </row>
     <row r="317">
@@ -13438,7 +13438,7 @@
         <v>19</v>
       </c>
       <c r="K317" t="n">
-        <v>1.942989979952576</v>
+        <v>1.940030584544124</v>
       </c>
     </row>
     <row r="318">
@@ -13479,7 +13479,7 @@
         <v>19</v>
       </c>
       <c r="K318" t="n">
-        <v>2.009862509617116</v>
+        <v>2.009504482132826</v>
       </c>
     </row>
     <row r="319">
@@ -13520,7 +13520,7 @@
         <v>19</v>
       </c>
       <c r="K319" t="n">
-        <v>2.009862509617116</v>
+        <v>2.009504482132826</v>
       </c>
     </row>
     <row r="320">
@@ -13561,7 +13561,7 @@
         <v>19</v>
       </c>
       <c r="K320" t="n">
-        <v>2.009862509617116</v>
+        <v>2.009504482132826</v>
       </c>
     </row>
     <row r="321">
@@ -13602,7 +13602,7 @@
         <v>19</v>
       </c>
       <c r="K321" t="n">
-        <v>1.983855882766451</v>
+        <v>1.985875892760085</v>
       </c>
     </row>
     <row r="322">
@@ -13643,7 +13643,7 @@
         <v>19</v>
       </c>
       <c r="K322" t="n">
-        <v>1.89423740544418</v>
+        <v>1.896293117472593</v>
       </c>
     </row>
     <row r="323">
@@ -13684,7 +13684,7 @@
         <v>19</v>
       </c>
       <c r="K323" t="n">
-        <v>1.851991922366913</v>
+        <v>1.852248863281735</v>
       </c>
     </row>
     <row r="324">
@@ -13725,7 +13725,7 @@
         <v>19</v>
       </c>
       <c r="K324" t="n">
-        <v>1.838373601298742</v>
+        <v>1.838305173733485</v>
       </c>
     </row>
     <row r="325">
@@ -13766,7 +13766,7 @@
         <v>19</v>
       </c>
       <c r="K325" t="n">
-        <v>1.856146432224067</v>
+        <v>1.853320858816376</v>
       </c>
     </row>
     <row r="326">
@@ -13807,7 +13807,7 @@
         <v>19</v>
       </c>
       <c r="K326" t="n">
-        <v>1.921307457076521</v>
+        <v>1.982299191174079</v>
       </c>
     </row>
     <row r="327">
@@ -13848,7 +13848,7 @@
         <v>19</v>
       </c>
       <c r="K327" t="n">
-        <v>2.051506057056442</v>
+        <v>2.04794602095187</v>
       </c>
     </row>
     <row r="328">
@@ -13889,7 +13889,7 @@
         <v>19</v>
       </c>
       <c r="K328" t="n">
-        <v>2.447242213919967</v>
+        <v>2.443407994656374</v>
       </c>
     </row>
     <row r="329">
@@ -13930,7 +13930,7 @@
         <v>19</v>
       </c>
       <c r="K329" t="n">
-        <v>2.447242213919967</v>
+        <v>2.443407994656374</v>
       </c>
     </row>
     <row r="330">
@@ -13971,7 +13971,7 @@
         <v>19</v>
       </c>
       <c r="K330" t="n">
-        <v>2.545084214334234</v>
+        <v>2.549884915528237</v>
       </c>
     </row>
     <row r="331">
@@ -14012,7 +14012,7 @@
         <v>19</v>
       </c>
       <c r="K331" t="n">
-        <v>2.505965983456013</v>
+        <v>2.515610614421037</v>
       </c>
     </row>
     <row r="332">
@@ -14053,7 +14053,7 @@
         <v>19</v>
       </c>
       <c r="K332" t="n">
-        <v>2.505965983456013</v>
+        <v>2.515610614421037</v>
       </c>
     </row>
     <row r="333">
@@ -14094,7 +14094,7 @@
         <v>19</v>
       </c>
       <c r="K333" t="n">
-        <v>2.180615655185912</v>
+        <v>2.183354126629911</v>
       </c>
     </row>
     <row r="334">
@@ -14135,7 +14135,7 @@
         <v>19</v>
       </c>
       <c r="K334" t="n">
-        <v>2.180615655185912</v>
+        <v>2.183354126629911</v>
       </c>
     </row>
     <row r="335">
@@ -14176,7 +14176,7 @@
         <v>19</v>
       </c>
       <c r="K335" t="n">
-        <v>2.180615655185912</v>
+        <v>2.183354126629911</v>
       </c>
     </row>
     <row r="336">
@@ -14217,7 +14217,7 @@
         <v>19</v>
       </c>
       <c r="K336" t="n">
-        <v>1.851446367687686</v>
+        <v>1.859191928112375</v>
       </c>
     </row>
     <row r="337">
@@ -14258,7 +14258,7 @@
         <v>19</v>
       </c>
       <c r="K337" t="n">
-        <v>1.851446367687686</v>
+        <v>1.859191928112375</v>
       </c>
     </row>
     <row r="338">
@@ -14299,7 +14299,7 @@
         <v>19</v>
       </c>
       <c r="K338" t="n">
-        <v>1.799395231474207</v>
+        <v>1.799629399999197</v>
       </c>
     </row>
     <row r="339">
@@ -14340,7 +14340,7 @@
         <v>19</v>
       </c>
       <c r="K339" t="n">
-        <v>1.791233266124873</v>
+        <v>1.791536139738593</v>
       </c>
     </row>
     <row r="340">
@@ -14381,7 +14381,7 @@
         <v>19</v>
       </c>
       <c r="K340" t="n">
-        <v>1.736680294836873</v>
+        <v>1.73791170095983</v>
       </c>
     </row>
     <row r="341">
@@ -14422,7 +14422,7 @@
         <v>19</v>
       </c>
       <c r="K341" t="n">
-        <v>1.723197987840439</v>
+        <v>1.723019297212971</v>
       </c>
     </row>
     <row r="342">
@@ -14463,7 +14463,7 @@
         <v>19</v>
       </c>
       <c r="K342" t="n">
-        <v>1.748045085521076</v>
+        <v>1.747458052244561</v>
       </c>
     </row>
     <row r="343">
@@ -14504,7 +14504,7 @@
         <v>19</v>
       </c>
       <c r="K343" t="n">
-        <v>1.818587736262817</v>
+        <v>1.81703469397588</v>
       </c>
     </row>
     <row r="344">
@@ -14545,7 +14545,7 @@
         <v>19</v>
       </c>
       <c r="K344" t="n">
-        <v>1.877345161450887</v>
+        <v>1.877711880185857</v>
       </c>
     </row>
     <row r="345">
@@ -14586,7 +14586,7 @@
         <v>19</v>
       </c>
       <c r="K345" t="n">
-        <v>1.877345161450887</v>
+        <v>1.877711880185857</v>
       </c>
     </row>
     <row r="346">
@@ -14627,7 +14627,7 @@
         <v>19</v>
       </c>
       <c r="K346" t="n">
-        <v>1.852286471695957</v>
+        <v>1.85302471279004</v>
       </c>
     </row>
     <row r="347">
@@ -14668,7 +14668,7 @@
         <v>19</v>
       </c>
       <c r="K347" t="n">
-        <v>1.852286471695957</v>
+        <v>1.85302471279004</v>
       </c>
     </row>
     <row r="348">
@@ -14709,7 +14709,7 @@
         <v>19</v>
       </c>
       <c r="K348" t="n">
-        <v>1.826802546691543</v>
+        <v>1.827207692162381</v>
       </c>
     </row>
     <row r="349">
@@ -14750,7 +14750,7 @@
         <v>19</v>
       </c>
       <c r="K349" t="n">
-        <v>1.740874112983046</v>
+        <v>1.741396904773116</v>
       </c>
     </row>
     <row r="350">
@@ -14791,7 +14791,7 @@
         <v>19</v>
       </c>
       <c r="K350" t="n">
-        <v>1.740874112983046</v>
+        <v>1.741396904773116</v>
       </c>
     </row>
     <row r="351">
@@ -14832,7 +14832,7 @@
         <v>19</v>
       </c>
       <c r="K351" t="n">
-        <v>1.710122181613697</v>
+        <v>1.70721398835612</v>
       </c>
     </row>
     <row r="352">
@@ -14873,7 +14873,7 @@
         <v>19</v>
       </c>
       <c r="K352" t="n">
-        <v>1.710122181613697</v>
+        <v>1.70721398835612</v>
       </c>
     </row>
     <row r="353">
@@ -14914,7 +14914,7 @@
         <v>19</v>
       </c>
       <c r="K353" t="n">
-        <v>1.711577156527548</v>
+        <v>1.711485397496341</v>
       </c>
     </row>
     <row r="354">
@@ -14955,7 +14955,7 @@
         <v>19</v>
       </c>
       <c r="K354" t="n">
-        <v>1.711577156527548</v>
+        <v>1.711485397496341</v>
       </c>
     </row>
     <row r="355">
@@ -14996,7 +14996,7 @@
         <v>19</v>
       </c>
       <c r="K355" t="n">
-        <v>1.766102214961997</v>
+        <v>1.765759130171297</v>
       </c>
     </row>
     <row r="356">
@@ -15037,7 +15037,7 @@
         <v>19</v>
       </c>
       <c r="K356" t="n">
-        <v>1.771368858762072</v>
+        <v>1.771160104429308</v>
       </c>
     </row>
     <row r="357">
@@ -15078,7 +15078,7 @@
         <v>19</v>
       </c>
       <c r="K357" t="n">
-        <v>1.771368858762072</v>
+        <v>1.771160104429308</v>
       </c>
     </row>
     <row r="358">
@@ -15119,7 +15119,7 @@
         <v>19</v>
       </c>
       <c r="K358" t="n">
-        <v>1.766702503247439</v>
+        <v>1.766837974227204</v>
       </c>
     </row>
     <row r="359">
@@ -15160,7 +15160,7 @@
         <v>19</v>
       </c>
       <c r="K359" t="n">
-        <v>1.766574228880781</v>
+        <v>1.766310722912269</v>
       </c>
     </row>
     <row r="360">
@@ -15201,7 +15201,7 @@
         <v>19</v>
       </c>
       <c r="K360" t="n">
-        <v>1.774435479572062</v>
+        <v>1.774364054429187</v>
       </c>
     </row>
     <row r="361">
@@ -15242,7 +15242,7 @@
         <v>19</v>
       </c>
       <c r="K361" t="n">
-        <v>1.732280004502077</v>
+        <v>1.733184250577489</v>
       </c>
     </row>
     <row r="362">
@@ -15283,7 +15283,7 @@
         <v>19</v>
       </c>
       <c r="K362" t="n">
-        <v>1.732280004502077</v>
+        <v>1.733184250577489</v>
       </c>
     </row>
     <row r="363">
@@ -15324,7 +15324,7 @@
         <v>19</v>
       </c>
       <c r="K363" t="n">
-        <v>1.62719532224214</v>
+        <v>1.627379709277815</v>
       </c>
     </row>
     <row r="364">
@@ -15365,7 +15365,7 @@
         <v>19</v>
       </c>
       <c r="K364" t="n">
-        <v>1.576373337863897</v>
+        <v>1.576971415263466</v>
       </c>
     </row>
     <row r="365">
@@ -15406,7 +15406,7 @@
         <v>19</v>
       </c>
       <c r="K365" t="n">
-        <v>1.576373337863897</v>
+        <v>1.576971415263466</v>
       </c>
     </row>
     <row r="366">
@@ -15447,7 +15447,7 @@
         <v>19</v>
       </c>
       <c r="K366" t="n">
-        <v>1.545949156847088</v>
+        <v>1.546709993108456</v>
       </c>
     </row>
     <row r="367">
@@ -15488,7 +15488,7 @@
         <v>19</v>
       </c>
       <c r="K367" t="n">
-        <v>1.455643529422251</v>
+        <v>1.455745858428015</v>
       </c>
     </row>
     <row r="368">
@@ -15529,7 +15529,7 @@
         <v>19</v>
       </c>
       <c r="K368" t="n">
-        <v>1.455643529422251</v>
+        <v>1.455745858428015</v>
       </c>
     </row>
     <row r="369">
@@ -15570,7 +15570,7 @@
         <v>19</v>
       </c>
       <c r="K369" t="n">
-        <v>1.513656614830826</v>
+        <v>1.512718401098489</v>
       </c>
     </row>
     <row r="370">
@@ -15611,7 +15611,7 @@
         <v>19</v>
       </c>
       <c r="K370" t="n">
-        <v>1.537827554966075</v>
+        <v>1.537679077043461</v>
       </c>
     </row>
     <row r="371">
@@ -15652,7 +15652,7 @@
         <v>19</v>
       </c>
       <c r="K371" t="n">
-        <v>1.55323201555771</v>
+        <v>1.553094941268011</v>
       </c>
     </row>
     <row r="372">
@@ -15693,7 +15693,7 @@
         <v>19</v>
       </c>
       <c r="K372" t="n">
-        <v>1.585928827959317</v>
+        <v>1.586420630939783</v>
       </c>
     </row>
     <row r="373">
@@ -15734,7 +15734,7 @@
         <v>19</v>
       </c>
       <c r="K373" t="n">
-        <v>1.585928827959317</v>
+        <v>1.586420630939783</v>
       </c>
     </row>
     <row r="374">
@@ -15775,7 +15775,7 @@
         <v>19</v>
       </c>
       <c r="K374" t="n">
-        <v>1.618895628870281</v>
+        <v>1.621844784123741</v>
       </c>
     </row>
     <row r="375">
@@ -15816,7 +15816,7 @@
         <v>19</v>
       </c>
       <c r="K375" t="n">
-        <v>1.629324585663673</v>
+        <v>1.630523656714317</v>
       </c>
     </row>
     <row r="376">
@@ -15857,7 +15857,7 @@
         <v>19</v>
       </c>
       <c r="K376" t="n">
-        <v>1.629324585663673</v>
+        <v>1.630523656714317</v>
       </c>
     </row>
     <row r="377">
@@ -15898,7 +15898,7 @@
         <v>19</v>
       </c>
       <c r="K377" t="n">
-        <v>1.709482026442248</v>
+        <v>1.709221231040555</v>
       </c>
     </row>
     <row r="378">
@@ -15939,7 +15939,7 @@
         <v>19</v>
       </c>
       <c r="K378" t="n">
-        <v>1.777237080477371</v>
+        <v>1.776931775524405</v>
       </c>
     </row>
     <row r="379">
@@ -15980,7 +15980,7 @@
         <v>19</v>
       </c>
       <c r="K379" t="n">
-        <v>1.94502448900215</v>
+        <v>1.944101229887065</v>
       </c>
     </row>
     <row r="380">
@@ -16021,7 +16021,7 @@
         <v>19</v>
       </c>
       <c r="K380" t="n">
-        <v>2.254065088468395</v>
+        <v>2.252557411164326</v>
       </c>
     </row>
     <row r="381">
@@ -16062,7 +16062,7 @@
         <v>19</v>
       </c>
       <c r="K381" t="n">
-        <v>2.254065088468395</v>
+        <v>2.252557411164326</v>
       </c>
     </row>
     <row r="382">
@@ -16103,7 +16103,7 @@
         <v>19</v>
       </c>
       <c r="K382" t="n">
-        <v>2.64070903816169</v>
+        <v>2.639858195591371</v>
       </c>
     </row>
     <row r="383">
@@ -16144,7 +16144,7 @@
         <v>19</v>
       </c>
       <c r="K383" t="n">
-        <v>2.702038020387838</v>
+        <v>2.701624208738097</v>
       </c>
     </row>
     <row r="384">
@@ -16185,7 +16185,7 @@
         <v>19</v>
       </c>
       <c r="K384" t="n">
-        <v>2.711497583780482</v>
+        <v>2.711774058943635</v>
       </c>
     </row>
     <row r="385">
@@ -16226,7 +16226,7 @@
         <v>19</v>
       </c>
       <c r="K385" t="n">
-        <v>2.686991605598184</v>
+        <v>2.687167658734501</v>
       </c>
     </row>
     <row r="386">
@@ -16267,7 +16267,7 @@
         <v>19</v>
       </c>
       <c r="K386" t="n">
-        <v>2.689100043028871</v>
+        <v>2.688905230625763</v>
       </c>
     </row>
     <row r="387">
@@ -16308,7 +16308,7 @@
         <v>19</v>
       </c>
       <c r="K387" t="n">
-        <v>2.710390854765613</v>
+        <v>2.710182699723763</v>
       </c>
     </row>
     <row r="388">
@@ -16349,7 +16349,7 @@
         <v>19</v>
       </c>
       <c r="K388" t="n">
-        <v>2.713051804903709</v>
+        <v>2.713253552305668</v>
       </c>
     </row>
     <row r="389">
@@ -16390,7 +16390,7 @@
         <v>19</v>
       </c>
       <c r="K389" t="n">
-        <v>2.713051804903709</v>
+        <v>2.676847107482138</v>
       </c>
     </row>
     <row r="390">
@@ -16431,7 +16431,7 @@
         <v>19</v>
       </c>
       <c r="K390" t="n">
-        <v>2.613986092754168</v>
+        <v>2.61458280684209</v>
       </c>
     </row>
     <row r="391">
@@ -16472,7 +16472,7 @@
         <v>19</v>
       </c>
       <c r="K391" t="n">
-        <v>2.531283790938132</v>
+        <v>2.532011700514746</v>
       </c>
     </row>
     <row r="392">
@@ -16513,7 +16513,7 @@
         <v>19</v>
       </c>
       <c r="K392" t="n">
-        <v>2.531283790938132</v>
+        <v>2.532011700514746</v>
       </c>
     </row>
     <row r="393">
@@ -16554,7 +16554,7 @@
         <v>19</v>
       </c>
       <c r="K393" t="n">
-        <v>2.283913990622641</v>
+        <v>2.2849674435088</v>
       </c>
     </row>
     <row r="394">
@@ -16595,7 +16595,7 @@
         <v>19</v>
       </c>
       <c r="K394" t="n">
-        <v>2.283913990622641</v>
+        <v>2.2849674435088</v>
       </c>
     </row>
     <row r="395">
@@ -16636,7 +16636,7 @@
         <v>19</v>
       </c>
       <c r="K395" t="n">
-        <v>2.283913990622641</v>
+        <v>2.2849674435088</v>
       </c>
     </row>
     <row r="396">
@@ -16677,7 +16677,7 @@
         <v>19</v>
       </c>
       <c r="K396" t="n">
-        <v>2.027584848581108</v>
+        <v>2.028427960578887</v>
       </c>
     </row>
     <row r="397">
@@ -16718,7 +16718,7 @@
         <v>19</v>
       </c>
       <c r="K397" t="n">
-        <v>2.027584848581108</v>
+        <v>2.028427960578887</v>
       </c>
     </row>
     <row r="398">
@@ -16759,7 +16759,7 @@
         <v>19</v>
       </c>
       <c r="K398" t="n">
-        <v>1.923658603643235</v>
+        <v>1.924205377232477</v>
       </c>
     </row>
     <row r="399">
@@ -16800,7 +16800,7 @@
         <v>19</v>
       </c>
       <c r="K399" t="n">
-        <v>1.923658603643235</v>
+        <v>1.924205377232477</v>
       </c>
     </row>
     <row r="400">
@@ -16841,7 +16841,7 @@
         <v>19</v>
       </c>
       <c r="K400" t="n">
-        <v>1.923658603643235</v>
+        <v>1.924205377232477</v>
       </c>
     </row>
     <row r="401">
@@ -16882,7 +16882,7 @@
         <v>19</v>
       </c>
       <c r="K401" t="n">
-        <v>1.669870889927171</v>
+        <v>1.670024067961148</v>
       </c>
     </row>
     <row r="402">
@@ -16923,7 +16923,7 @@
         <v>19</v>
       </c>
       <c r="K402" t="n">
-        <v>1.646359204252003</v>
+        <v>1.646500654948282</v>
       </c>
     </row>
     <row r="403">
@@ -16964,7 +16964,7 @@
         <v>19</v>
       </c>
       <c r="K403" t="n">
-        <v>1.622414088845661</v>
+        <v>1.622500182418778</v>
       </c>
     </row>
     <row r="404">
@@ -17005,7 +17005,7 @@
         <v>19</v>
       </c>
       <c r="K404" t="n">
-        <v>2.040047376880401</v>
+        <v>2.039411625018872</v>
       </c>
     </row>
     <row r="405">
@@ -17046,7 +17046,7 @@
         <v>19</v>
       </c>
       <c r="K405" t="n">
-        <v>2.326372732195173</v>
+        <v>2.325818972321627</v>
       </c>
     </row>
     <row r="406">
@@ -17087,7 +17087,7 @@
         <v>19</v>
       </c>
       <c r="K406" t="n">
-        <v>2.458528621530921</v>
+        <v>2.458100163175225</v>
       </c>
     </row>
     <row r="407">
@@ -17128,7 +17128,7 @@
         <v>19</v>
       </c>
       <c r="K407" t="n">
-        <v>2.637721533265895</v>
+        <v>2.63778884709392</v>
       </c>
     </row>
     <row r="408">
@@ -17169,7 +17169,7 @@
         <v>19</v>
       </c>
       <c r="K408" t="n">
-        <v>2.575180276561596</v>
+        <v>2.575504148148231</v>
       </c>
     </row>
     <row r="409">
@@ -17210,7 +17210,7 @@
         <v>19</v>
       </c>
       <c r="K409" t="n">
-        <v>2.437303864207278</v>
+        <v>2.437827921825554</v>
       </c>
     </row>
     <row r="410">
@@ -17251,7 +17251,7 @@
         <v>19</v>
       </c>
       <c r="K410" t="n">
-        <v>2.264208077156312</v>
+        <v>2.264799592500081</v>
       </c>
     </row>
     <row r="411">
@@ -17292,7 +17292,7 @@
         <v>19</v>
       </c>
       <c r="K411" t="n">
-        <v>2.264208077156312</v>
+        <v>2.264799592500081</v>
       </c>
     </row>
     <row r="412">
@@ -17333,7 +17333,7 @@
         <v>19</v>
       </c>
       <c r="K412" t="n">
-        <v>1.199065355203013</v>
+        <v>1.19959856270633</v>
       </c>
     </row>
     <row r="413">
@@ -17374,7 +17374,7 @@
         <v>19</v>
       </c>
       <c r="K413" t="n">
-        <v>1.199065355203013</v>
+        <v>1.19959856270633</v>
       </c>
     </row>
     <row r="414">
@@ -17415,7 +17415,7 @@
         <v>19</v>
       </c>
       <c r="K414" t="n">
-        <v>1.010187972691869</v>
+        <v>1.010492998885309</v>
       </c>
     </row>
     <row r="415">
@@ -17456,7 +17456,7 @@
         <v>19</v>
       </c>
       <c r="K415" t="n">
-        <v>0.6943993063449685</v>
+        <v>0.6946604151957111</v>
       </c>
     </row>
     <row r="416">
@@ -17497,7 +17497,7 @@
         <v>19</v>
       </c>
       <c r="K416" t="n">
-        <v>0.6943993063449685</v>
+        <v>0.6946604151957111</v>
       </c>
     </row>
     <row r="417">
@@ -17538,7 +17538,7 @@
         <v>19</v>
       </c>
       <c r="K417" t="n">
-        <v>0.4671261519470916</v>
+        <v>0.4670818633884443</v>
       </c>
     </row>
     <row r="418">
@@ -17579,7 +17579,7 @@
         <v>19</v>
       </c>
       <c r="K418" t="n">
-        <v>0.4892300935702013</v>
+        <v>0.4892345910357476</v>
       </c>
     </row>
     <row r="419">
@@ -17620,7 +17620,7 @@
         <v>19</v>
       </c>
       <c r="K419" t="n">
-        <v>0.1972305626343492</v>
+        <v>0.1971870344553905</v>
       </c>
     </row>
   </sheetData>
